--- a/product_selector_out/STM32H7R7-7S7.xlsx
+++ b/product_selector_out/STM32H7R7-7S7.xlsx
@@ -42,7 +42,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -61,17 +61,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -90,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
@@ -103,8 +93,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1338,7 +1326,7 @@
       </c>
       <c r="BO12" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h7r3a8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1663,7 @@
       </c>
       <c r="BO13" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h7r3a8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2000,7 @@
       </c>
       <c r="BO14" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h7r3a8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2337,7 @@
       </c>
       <c r="BO15" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h7r3a8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2674,7 @@
       </c>
       <c r="BO16" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h7s3a8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3011,7 @@
       </c>
       <c r="BO17" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h7s3a8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3348,7 @@
       </c>
       <c r="BO18" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h7s3a8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3685,7 @@
       </c>
       <c r="BO19" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32h7s3a8.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4323,9 +4311,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -4363,7 +4351,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="M12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4373,7 +4361,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
+      <c r="O12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4388,14 +4376,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R12" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S12" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T12" s="6" t="inlineStr">
@@ -4413,12 +4401,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X12" s="8" t="inlineStr">
+      <c r="W12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4428,7 +4416,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Z12" s="8" t="inlineStr">
+      <c r="Z12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4438,7 +4426,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AB12" s="8" t="inlineStr">
+      <c r="AB12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4448,7 +4436,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD12" s="8" t="inlineStr">
+      <c r="AD12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4463,12 +4451,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH12" s="8" t="inlineStr">
+      <c r="AG12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4498,12 +4486,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO12" s="8" t="inlineStr">
+      <c r="AN12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4533,7 +4521,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU12" s="8" t="inlineStr">
+      <c r="AU12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4543,22 +4531,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW12" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY12" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ12" s="8" t="inlineStr">
+      <c r="AW12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4573,52 +4561,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK12" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL12" s="8" t="inlineStr">
+      <c r="BC12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL12" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4633,9 +4621,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -4660,9 +4648,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -4700,7 +4688,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M13" s="8" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4710,7 +4698,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O13" s="8" t="inlineStr">
+      <c r="O13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4725,14 +4713,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T13" s="6" t="inlineStr">
@@ -4750,12 +4738,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X13" s="8" t="inlineStr">
+      <c r="W13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4765,7 +4753,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Z13" s="8" t="inlineStr">
+      <c r="Z13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4775,7 +4763,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AB13" s="8" t="inlineStr">
+      <c r="AB13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4785,7 +4773,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD13" s="8" t="inlineStr">
+      <c r="AD13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4800,12 +4788,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH13" s="8" t="inlineStr">
+      <c r="AG13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4835,12 +4823,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO13" s="8" t="inlineStr">
+      <c r="AN13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4870,7 +4858,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU13" s="8" t="inlineStr">
+      <c r="AU13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4880,22 +4868,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ13" s="8" t="inlineStr">
+      <c r="AW13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4910,52 +4898,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL13" s="8" t="inlineStr">
+      <c r="BC13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL13" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4970,9 +4958,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO13" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -4997,9 +4985,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -5037,7 +5025,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M14" s="8" t="inlineStr">
+      <c r="M14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5047,7 +5035,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
+      <c r="O14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5062,14 +5050,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T14" s="6" t="inlineStr">
@@ -5087,12 +5075,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X14" s="8" t="inlineStr">
+      <c r="W14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5102,7 +5090,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Z14" s="8" t="inlineStr">
+      <c r="Z14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5112,7 +5100,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AB14" s="8" t="inlineStr">
+      <c r="AB14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5122,7 +5110,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD14" s="8" t="inlineStr">
+      <c r="AD14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5137,12 +5125,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH14" s="8" t="inlineStr">
+      <c r="AG14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5172,12 +5160,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO14" s="8" t="inlineStr">
+      <c r="AN14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5207,7 +5195,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU14" s="8" t="inlineStr">
+      <c r="AU14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5217,22 +5205,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ14" s="8" t="inlineStr">
+      <c r="AW14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5247,52 +5235,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL14" s="8" t="inlineStr">
+      <c r="BC14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL14" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5307,9 +5295,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO14" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -5334,9 +5322,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -5374,7 +5362,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M15" s="8" t="inlineStr">
+      <c r="M15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5384,7 +5372,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O15" s="8" t="inlineStr">
+      <c r="O15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5399,14 +5387,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T15" s="6" t="inlineStr">
@@ -5424,12 +5412,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X15" s="8" t="inlineStr">
+      <c r="W15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5439,7 +5427,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Z15" s="8" t="inlineStr">
+      <c r="Z15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5449,7 +5437,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AB15" s="8" t="inlineStr">
+      <c r="AB15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5459,7 +5447,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD15" s="8" t="inlineStr">
+      <c r="AD15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5474,12 +5462,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH15" s="8" t="inlineStr">
+      <c r="AG15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5509,12 +5497,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO15" s="8" t="inlineStr">
+      <c r="AN15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5544,7 +5532,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU15" s="8" t="inlineStr">
+      <c r="AU15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5554,22 +5542,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ15" s="8" t="inlineStr">
+      <c r="AW15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5584,52 +5572,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL15" s="8" t="inlineStr">
+      <c r="BC15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL15" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5644,9 +5632,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO15" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -5671,9 +5659,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -5711,7 +5699,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M16" s="8" t="inlineStr">
+      <c r="M16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5721,7 +5709,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O16" s="8" t="inlineStr">
+      <c r="O16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5736,14 +5724,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T16" s="6" t="inlineStr">
@@ -5761,12 +5749,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X16" s="8" t="inlineStr">
+      <c r="W16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5776,7 +5764,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Z16" s="8" t="inlineStr">
+      <c r="Z16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5786,7 +5774,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AB16" s="8" t="inlineStr">
+      <c r="AB16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5796,7 +5784,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD16" s="8" t="inlineStr">
+      <c r="AD16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5811,12 +5799,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH16" s="8" t="inlineStr">
+      <c r="AG16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5846,12 +5834,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO16" s="8" t="inlineStr">
+      <c r="AN16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5881,7 +5869,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU16" s="8" t="inlineStr">
+      <c r="AU16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5891,22 +5879,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ16" s="8" t="inlineStr">
+      <c r="AW16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5921,52 +5909,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL16" s="8" t="inlineStr">
+      <c r="BC16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL16" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5981,9 +5969,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO16" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -6008,9 +5996,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -6048,7 +6036,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M17" s="8" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6058,7 +6046,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O17" s="8" t="inlineStr">
+      <c r="O17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6073,14 +6061,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R17" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S17" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T17" s="6" t="inlineStr">
@@ -6098,12 +6086,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X17" s="8" t="inlineStr">
+      <c r="W17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6113,7 +6101,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Z17" s="8" t="inlineStr">
+      <c r="Z17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6133,7 +6121,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD17" s="8" t="inlineStr">
+      <c r="AD17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6148,12 +6136,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH17" s="8" t="inlineStr">
+      <c r="AG17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6183,12 +6171,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO17" s="8" t="inlineStr">
+      <c r="AN17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6218,7 +6206,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU17" s="8" t="inlineStr">
+      <c r="AU17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6228,22 +6216,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW17" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY17" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ17" s="8" t="inlineStr">
+      <c r="AW17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6258,52 +6246,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK17" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL17" s="8" t="inlineStr">
+      <c r="BC17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL17" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6318,9 +6306,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO17" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -6345,9 +6333,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -6385,7 +6373,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M18" s="8" t="inlineStr">
+      <c r="M18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6395,7 +6383,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O18" s="8" t="inlineStr">
+      <c r="O18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6410,14 +6398,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R18" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S18" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T18" s="6" t="inlineStr">
@@ -6435,12 +6423,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X18" s="8" t="inlineStr">
+      <c r="W18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6450,7 +6438,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Z18" s="8" t="inlineStr">
+      <c r="Z18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6460,7 +6448,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AB18" s="8" t="inlineStr">
+      <c r="AB18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6470,7 +6458,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD18" s="8" t="inlineStr">
+      <c r="AD18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6485,12 +6473,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH18" s="8" t="inlineStr">
+      <c r="AG18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6520,12 +6508,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO18" s="8" t="inlineStr">
+      <c r="AN18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6555,7 +6543,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU18" s="8" t="inlineStr">
+      <c r="AU18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6565,22 +6553,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW18" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY18" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ18" s="8" t="inlineStr">
+      <c r="AW18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6595,52 +6583,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL18" s="8" t="inlineStr">
+      <c r="BC18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL18" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6655,9 +6643,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO18" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -6682,9 +6670,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -6722,7 +6710,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M19" s="8" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6732,7 +6720,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O19" s="8" t="inlineStr">
+      <c r="O19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6747,14 +6735,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T19" s="6" t="inlineStr">
@@ -6772,12 +6760,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X19" s="8" t="inlineStr">
+      <c r="W19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6787,7 +6775,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Z19" s="8" t="inlineStr">
+      <c r="Z19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6797,7 +6785,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AB19" s="8" t="inlineStr">
+      <c r="AB19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6807,7 +6795,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD19" s="8" t="inlineStr">
+      <c r="AD19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6822,12 +6810,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH19" s="8" t="inlineStr">
+      <c r="AG19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6857,12 +6845,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO19" s="8" t="inlineStr">
+      <c r="AN19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6892,7 +6880,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU19" s="8" t="inlineStr">
+      <c r="AU19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6902,22 +6890,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ19" s="8" t="inlineStr">
+      <c r="AW19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AZ19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6932,52 +6920,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL19" s="8" t="inlineStr">
+      <c r="BC19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL19" s="7" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6992,9 +6980,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO19" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7013,7 +7001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7044,710 +7032,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>STM32H7R7A8</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>STM32H7R7A8</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>STM32H7R7A8</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>STM32H7R7A8</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Table 132. OTG_HS current consumption characteristics(1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>STM32H7R7Z8</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>STM32H7R7Z8</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>STM32H7R7Z8</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>STM32H7R7Z8</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Table 132. OTG_HS current consumption characteristics(1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>STM32H7R7I8</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>STM32H7R7I8</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>STM32H7R7I8</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>STM32H7R7I8</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Table 132. OTG_HS current consumption characteristics(1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>STM32H7R7L8</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>STM32H7R7L8</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Table 11. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>STM32H7R7L8</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>STM32H7R7L8</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Table 132. OTG_HS current consumption characteristics(1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>STM32H7S7Z8</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Table 13. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>STM32H7S7Z8</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Table 13. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>STM32H7S7Z8</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>STM32H7S7Z8</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Table 134. OTG_HS current consumption characteristics(1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>STM32H7S7I8</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Table 13. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>STM32H7S7I8</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Table 13. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>STM32H7S7I8</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>STM32H7S7I8</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Table 134. OTG_HS current consumption characteristics(1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>STM32H7S7L8</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Table 13. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>STM32H7S7L8</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Table 13. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>STM32H7S7L8</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>STM32H7S7L8</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Table 134. OTG_HS current consumption characteristics(1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>STM32H7S7A8</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Table 13. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>STM32H7S7A8</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Table 13. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>STM32H7S7A8</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Table 26. General operating conditions: V_DD min reads '1.71(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>STM32H7S7A8</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Table 134. OTG_HS current consumption characteristics(1)</t>
-        </is>
-      </c>
-    </row>
+    <row r="2"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/product_selector_out/STM32H7R7-7S7.xlsx
+++ b/product_selector_out/STM32H7R7-7S7.xlsx
@@ -42,7 +42,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -61,7 +61,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -80,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
@@ -93,6 +103,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1326,7 +1338,7 @@
       </c>
       <c r="BO12" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h7r3a8.pdf</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1675,7 @@
       </c>
       <c r="BO13" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h7r3a8.pdf</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2012,7 @@
       </c>
       <c r="BO14" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h7r3a8.pdf</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2349,7 @@
       </c>
       <c r="BO15" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h7r3a8.pdf</t>
         </is>
       </c>
     </row>
@@ -2674,7 +2686,7 @@
       </c>
       <c r="BO16" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h7s3a8.pdf</t>
         </is>
       </c>
     </row>
@@ -3011,7 +3023,7 @@
       </c>
       <c r="BO17" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h7s3a8.pdf</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3360,7 @@
       </c>
       <c r="BO18" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h7s3a8.pdf</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3697,7 @@
       </c>
       <c r="BO19" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32h7s3a8.pdf</t>
         </is>
       </c>
     </row>
@@ -4311,9 +4323,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -4351,7 +4363,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M12" s="7" t="inlineStr">
+      <c r="M12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4361,7 +4373,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O12" s="7" t="inlineStr">
+      <c r="O12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4376,14 +4388,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T12" s="6" t="inlineStr">
@@ -4401,12 +4413,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X12" s="7" t="inlineStr">
+      <c r="W12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4416,7 +4428,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Z12" s="7" t="inlineStr">
+      <c r="Z12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4426,7 +4438,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AB12" s="7" t="inlineStr">
+      <c r="AB12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4436,7 +4448,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD12" s="7" t="inlineStr">
+      <c r="AD12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4451,12 +4463,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH12" s="7" t="inlineStr">
+      <c r="AG12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4486,12 +4498,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO12" s="7" t="inlineStr">
+      <c r="AN12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4521,7 +4533,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU12" s="7" t="inlineStr">
+      <c r="AU12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4531,22 +4543,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ12" s="7" t="inlineStr">
+      <c r="AW12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AZ12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4561,52 +4573,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL12" s="7" t="inlineStr">
+      <c r="BC12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL12" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4621,9 +4633,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO12" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -4648,9 +4660,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -4688,7 +4700,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M13" s="7" t="inlineStr">
+      <c r="M13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4698,7 +4710,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O13" s="7" t="inlineStr">
+      <c r="O13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4713,14 +4725,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T13" s="6" t="inlineStr">
@@ -4738,12 +4750,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X13" s="7" t="inlineStr">
+      <c r="W13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4753,7 +4765,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Z13" s="7" t="inlineStr">
+      <c r="Z13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4763,7 +4775,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AB13" s="7" t="inlineStr">
+      <c r="AB13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4773,7 +4785,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD13" s="7" t="inlineStr">
+      <c r="AD13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4788,12 +4800,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH13" s="7" t="inlineStr">
+      <c r="AG13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4823,12 +4835,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO13" s="7" t="inlineStr">
+      <c r="AN13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4858,7 +4870,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU13" s="7" t="inlineStr">
+      <c r="AU13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4868,22 +4880,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ13" s="7" t="inlineStr">
+      <c r="AW13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AZ13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4898,52 +4910,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL13" s="7" t="inlineStr">
+      <c r="BC13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL13" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -4958,9 +4970,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO13" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -4985,9 +4997,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -5025,7 +5037,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M14" s="7" t="inlineStr">
+      <c r="M14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5035,7 +5047,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O14" s="7" t="inlineStr">
+      <c r="O14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5050,14 +5062,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T14" s="6" t="inlineStr">
@@ -5075,12 +5087,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X14" s="7" t="inlineStr">
+      <c r="W14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5090,7 +5102,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Z14" s="7" t="inlineStr">
+      <c r="Z14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5100,7 +5112,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AB14" s="7" t="inlineStr">
+      <c r="AB14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5110,7 +5122,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD14" s="7" t="inlineStr">
+      <c r="AD14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5125,12 +5137,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH14" s="7" t="inlineStr">
+      <c r="AG14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5160,12 +5172,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO14" s="7" t="inlineStr">
+      <c r="AN14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5195,7 +5207,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU14" s="7" t="inlineStr">
+      <c r="AU14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5205,22 +5217,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ14" s="7" t="inlineStr">
+      <c r="AW14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AZ14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5235,52 +5247,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL14" s="7" t="inlineStr">
+      <c r="BC14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL14" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5295,9 +5307,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO14" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -5322,9 +5334,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -5362,7 +5374,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M15" s="7" t="inlineStr">
+      <c r="M15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5372,7 +5384,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O15" s="7" t="inlineStr">
+      <c r="O15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5387,14 +5399,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T15" s="6" t="inlineStr">
@@ -5412,12 +5424,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X15" s="7" t="inlineStr">
+      <c r="W15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5427,7 +5439,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Z15" s="7" t="inlineStr">
+      <c r="Z15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5437,7 +5449,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AB15" s="7" t="inlineStr">
+      <c r="AB15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5447,7 +5459,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD15" s="7" t="inlineStr">
+      <c r="AD15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5462,12 +5474,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH15" s="7" t="inlineStr">
+      <c r="AG15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5497,12 +5509,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO15" s="7" t="inlineStr">
+      <c r="AN15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5532,7 +5544,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU15" s="7" t="inlineStr">
+      <c r="AU15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5542,22 +5554,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ15" s="7" t="inlineStr">
+      <c r="AW15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AZ15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5572,52 +5584,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL15" s="7" t="inlineStr">
+      <c r="BC15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL15" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5632,9 +5644,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO15" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -5659,9 +5671,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -5699,7 +5711,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M16" s="7" t="inlineStr">
+      <c r="M16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5709,7 +5721,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O16" s="7" t="inlineStr">
+      <c r="O16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5724,14 +5736,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T16" s="6" t="inlineStr">
@@ -5749,12 +5761,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X16" s="7" t="inlineStr">
+      <c r="W16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5764,7 +5776,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Z16" s="7" t="inlineStr">
+      <c r="Z16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5774,7 +5786,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AB16" s="7" t="inlineStr">
+      <c r="AB16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5784,7 +5796,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD16" s="7" t="inlineStr">
+      <c r="AD16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5799,12 +5811,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH16" s="7" t="inlineStr">
+      <c r="AG16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5834,12 +5846,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO16" s="7" t="inlineStr">
+      <c r="AN16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5869,7 +5881,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU16" s="7" t="inlineStr">
+      <c r="AU16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5879,22 +5891,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ16" s="7" t="inlineStr">
+      <c r="AW16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AZ16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5909,52 +5921,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL16" s="7" t="inlineStr">
+      <c r="BC16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL16" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -5969,9 +5981,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO16" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -5996,9 +6008,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -6036,7 +6048,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M17" s="7" t="inlineStr">
+      <c r="M17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6046,7 +6058,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O17" s="7" t="inlineStr">
+      <c r="O17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6061,14 +6073,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T17" s="6" t="inlineStr">
@@ -6086,12 +6098,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X17" s="7" t="inlineStr">
+      <c r="W17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6101,7 +6113,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Z17" s="7" t="inlineStr">
+      <c r="Z17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6121,7 +6133,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD17" s="7" t="inlineStr">
+      <c r="AD17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6136,12 +6148,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH17" s="7" t="inlineStr">
+      <c r="AG17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6171,12 +6183,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO17" s="7" t="inlineStr">
+      <c r="AN17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6206,7 +6218,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU17" s="7" t="inlineStr">
+      <c r="AU17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6216,22 +6228,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ17" s="7" t="inlineStr">
+      <c r="AW17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AZ17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6246,52 +6258,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL17" s="7" t="inlineStr">
+      <c r="BC17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL17" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6306,9 +6318,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO17" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -6333,9 +6345,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -6373,7 +6385,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M18" s="7" t="inlineStr">
+      <c r="M18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6383,7 +6395,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O18" s="7" t="inlineStr">
+      <c r="O18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6398,14 +6410,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T18" s="6" t="inlineStr">
@@ -6423,12 +6435,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X18" s="7" t="inlineStr">
+      <c r="W18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6438,7 +6450,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Z18" s="7" t="inlineStr">
+      <c r="Z18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6448,7 +6460,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AB18" s="7" t="inlineStr">
+      <c r="AB18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6458,7 +6470,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD18" s="7" t="inlineStr">
+      <c r="AD18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6473,12 +6485,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH18" s="7" t="inlineStr">
+      <c r="AG18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6508,12 +6520,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO18" s="7" t="inlineStr">
+      <c r="AN18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6543,7 +6555,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU18" s="7" t="inlineStr">
+      <c r="AU18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6553,22 +6565,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ18" s="7" t="inlineStr">
+      <c r="AW18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AZ18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6583,52 +6595,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL18" s="7" t="inlineStr">
+      <c r="BC18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL18" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6643,9 +6655,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO18" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -6670,9 +6682,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -6710,7 +6722,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="M19" s="7" t="inlineStr">
+      <c r="M19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6720,7 +6732,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="O19" s="7" t="inlineStr">
+      <c r="O19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6735,14 +6747,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T19" s="6" t="inlineStr">
@@ -6760,12 +6772,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="W19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="X19" s="7" t="inlineStr">
+      <c r="W19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="X19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6775,7 +6787,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="Z19" s="7" t="inlineStr">
+      <c r="Z19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6785,7 +6797,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AB19" s="7" t="inlineStr">
+      <c r="AB19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6795,7 +6807,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD19" s="7" t="inlineStr">
+      <c r="AD19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6810,12 +6822,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AH19" s="7" t="inlineStr">
+      <c r="AG19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6845,12 +6857,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AN19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AO19" s="7" t="inlineStr">
+      <c r="AN19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AO19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6880,7 +6892,7 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AU19" s="7" t="inlineStr">
+      <c r="AU19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6890,22 +6902,22 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="AZ19" s="7" t="inlineStr">
+      <c r="AW19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AZ19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6920,52 +6932,52 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BC19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BD19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BE19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BF19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BG19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BH19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BI19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BJ19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BK19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="BL19" s="7" t="inlineStr">
+      <c r="BC19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BD19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BE19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BF19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BG19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BH19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BI19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BJ19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BK19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BL19" s="8" t="inlineStr">
         <is>
           <t>UNAVAILABLE</t>
         </is>
@@ -6980,9 +6992,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO19" s="7" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BO19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -7001,7 +7013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7032,7 +7044,886 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>STM32H7R7A8</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>STM32H7R7A8</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>STM32H7R7A8</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>STM32H7R7A8</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>STM32H7R7A8</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Table 132. OTG_HS current consumption characteristics(1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>STM32H7R7Z8</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>STM32H7R7Z8</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>STM32H7R7Z8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>STM32H7R7Z8</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>STM32H7R7Z8</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Table 132. OTG_HS current consumption characteristics(1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>STM32H7R7I8</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>STM32H7R7I8</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>STM32H7R7I8</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>STM32H7R7I8</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>STM32H7R7I8</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Table 132. OTG_HS current consumption characteristics(1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>STM32H7R7L8</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>STM32H7R7L8</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Table 11. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>STM32H7R7L8</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>STM32H7R7L8</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>STM32H7R7L8</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Table 132. OTG_HS current consumption characteristics(1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>STM32H7S7Z8</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Table 13. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>STM32H7S7Z8</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Table 13. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>STM32H7S7Z8</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>STM32H7S7Z8</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>STM32H7S7Z8</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Table 134. OTG_HS current consumption characteristics(1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>STM32H7S7I8</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Table 13. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>STM32H7S7I8</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Table 13. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>STM32H7S7I8</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>STM32H7S7I8</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>STM32H7S7I8</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Table 134. OTG_HS current consumption characteristics(1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>STM32H7S7L8</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Table 13. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>STM32H7S7L8</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Table 13. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>STM32H7S7L8</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>STM32H7S7L8</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>STM32H7S7L8</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Table 134. OTG_HS current consumption characteristics(1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>STM32H7S7A8</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Table 13. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>STM32H7S7A8</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Table 13. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>STM32H7S7A8</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD min reads '1.71(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>STM32H7S7A8</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) max</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Table 26. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>STM32H7S7A8</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Table 134. OTG_HS current consumption characteristics(1)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/product_selector_out/STM32H7R7-7S7.xlsx
+++ b/product_selector_out/STM32H7R7-7S7.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO19"/>
+  <dimension ref="A1:BP19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.6640625" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,8 @@
     <col width="21.765625" customWidth="1" min="64" max="64"/>
     <col width="18" customWidth="1" min="65" max="65"/>
     <col width="18" customWidth="1" min="66" max="66"/>
-    <col width="52" customWidth="1" min="67" max="67"/>
+    <col width="18" customWidth="1" min="67" max="67"/>
+    <col width="52" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -907,6 +908,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -1004,6 +1010,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1338,6 +1345,11 @@
       </c>
       <c r="BO12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h7r3a8.pdf</t>
         </is>
       </c>
@@ -1675,6 +1687,11 @@
       </c>
       <c r="BO13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h7r3a8.pdf</t>
         </is>
       </c>
@@ -2012,6 +2029,11 @@
       </c>
       <c r="BO14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h7r3a8.pdf</t>
         </is>
       </c>
@@ -2349,6 +2371,11 @@
       </c>
       <c r="BO15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h7r3a8.pdf</t>
         </is>
       </c>
@@ -2686,6 +2713,11 @@
       </c>
       <c r="BO16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h7s3a8.pdf</t>
         </is>
       </c>
@@ -3023,6 +3055,11 @@
       </c>
       <c r="BO17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h7s3a8.pdf</t>
         </is>
       </c>
@@ -3360,6 +3397,11 @@
       </c>
       <c r="BO18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h7s3a8.pdf</t>
         </is>
       </c>
@@ -3697,12 +3739,17 @@
       </c>
       <c r="BO19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32h7s3a8.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="67">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -3725,12 +3772,14 @@
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
     <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="A9:BP9"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="A1:BP8"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -3745,9 +3794,8 @@
     <mergeCell ref="BH10:BH11"/>
     <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="A9:BO9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="AL10:AL11"/>
@@ -3791,7 +3839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO19"/>
+  <dimension ref="A1:BP19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3861,6 +3909,7 @@
     <col width="16" customWidth="1" min="65" max="65"/>
     <col width="16" customWidth="1" min="66" max="66"/>
     <col width="16" customWidth="1" min="67" max="67"/>
+    <col width="16" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4204,6 +4253,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -4301,6 +4355,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -4633,7 +4688,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO12" s="6" t="inlineStr">
+      <c r="BO12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -4970,7 +5030,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO13" s="6" t="inlineStr">
+      <c r="BO13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5307,7 +5372,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO14" s="6" t="inlineStr">
+      <c r="BO14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5644,7 +5714,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO15" s="6" t="inlineStr">
+      <c r="BO15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5981,7 +6056,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO16" s="6" t="inlineStr">
+      <c r="BO16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6318,7 +6398,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO17" s="6" t="inlineStr">
+      <c r="BO17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6655,7 +6740,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO18" s="6" t="inlineStr">
+      <c r="BO18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6992,7 +7082,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO19" s="6" t="inlineStr">
+      <c r="BO19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7000,8 +7095,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BO9"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="A1:BP8"/>
+    <mergeCell ref="A9:BP9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
